--- a/data/raw/australiansuper_official.xlsx
+++ b/data/raw/australiansuper_official.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://australiansuper.sharepoint.com/teams/FO-FRSRI/PA/COMMUNICATION/Option Level Performance/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{28288E02-60D4-4F0C-9F2C-49763F0B1D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7289FC35-663C-4D41-B07D-EC06B41E0E7F}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{997712A8-9C01-4629-B7D1-4B99C1476E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FEFF89B-52D8-4958-A6F2-0931E59F8E98}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -178,7 +178,7 @@
     <definedName name="wrn.Mid._.Month." hidden="1">{"PERFORMANCE",#N/A,FALSE,"Summary";"EQUITIES",#N/A,FALSE,"Equity";"Fixed Interest",#N/A,FALSE,"Fixed Interest";"Total Fund",#N/A,FALSE,"Total Fund"}</definedName>
     <definedName name="wrn.PACKAGE." hidden="1">{"PERFORMANCE",#N/A,FALSE,"Summary";"EQUITIES",#N/A,FALSE,"Equity";"FIXED INTEREST",#N/A,FALSE,"Fixed Interest";"RECONCILIATION",#N/A,FALSE,"Summary";"CROSS REFERENCE",#N/A,FALSE,"Summary"}</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -506,7 +506,16 @@
     </r>
   </si>
   <si>
-    <t>Investment returns are not guaranteed. Past performance is not a reliable indicator of future returns.  All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
+    <t>AustralianSuper investment returns are based on crediting rates, which are returns less investment fees and costs, transaction costs, the percentage-based administration fee deducted from returns from 1 April 2020 to 2 September 2022 and taxes. Investment returns aren’t guaranteed. Past performance isn’t a reliable indicator of future returns. All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
+  </si>
+  <si>
+    <t>Returns from equivalent options of the ARF and STA super funds are used in calculating returns for periods that begin before 1 July 2006.</t>
+  </si>
+  <si>
+    <t>For TTR Income accounts, the investment return is based on the crediting rate for super (accumulation) options. From 1 April 2020 to 2 September 2022 the crediting rate includes an administration fee that was deducted from investment returns for super (accumulation) accounts. TTR Income accounts have been adjusted to refund the administration fee deducted from investment returns.</t>
+  </si>
+  <si>
+    <t>Report generated on 02 September 2026</t>
   </si>
   <si>
     <r>
@@ -586,6 +595,9 @@
   </si>
   <si>
     <t>Choice Income AustralianSuper investment returns are based on crediting rates, which are returns less investment fees and costs, transaction costs and taxes.</t>
+  </si>
+  <si>
+    <t>Investment returns are not guaranteed. Past performance is not a reliable indicator of future returns.  All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
   </si>
   <si>
     <r>
@@ -649,18 +661,6 @@
       <t>. AustralianSuper Pty Ltd, ABN 94 006 457 987, AFSL 233788, Trustee of AustralianSuper ABN 65 714 394 898.</t>
     </r>
   </si>
-  <si>
-    <t>AustralianSuper investment returns are based on crediting rates, which are returns less investment fees and costs, transaction costs, the percentage-based administration fee deducted from returns from 1 April 2020 to 2 September 2022 and taxes. Investment returns aren’t guaranteed. Past performance isn’t a reliable indicator of future returns. All care is taken to ensure this information is correct at the date of publication. Any errors or misprints will be corrected by the Trustee in later reports.</t>
-  </si>
-  <si>
-    <t>Returns from equivalent options of the ARF and STA super funds are used in calculating returns for periods that begin before 1 July 2006.</t>
-  </si>
-  <si>
-    <t>For TTR Income accounts, the investment return is based on the crediting rate for super (accumulation) options. From 1 April 2020 to 2 September 2022 the crediting rate includes an administration fee that was deducted from investment returns for super (accumulation) accounts. TTR Income accounts have been adjusted to refund the administration fee deducted from investment returns.</t>
-  </si>
-  <si>
-    <t>Report generated on 04 August 2026</t>
-  </si>
 </sst>
 </file>
 
@@ -671,9 +671,9 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="mmm\ yy"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1166,25 +1166,25 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="3" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="3" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1196,19 +1196,19 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="3" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="3" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1226,7 +1226,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="3" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1235,18 +1235,18 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1265,7 +1265,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1358,7 +1358,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>709705</xdr:colOff>
+      <xdr:colOff>643030</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>193061</xdr:rowOff>
     </xdr:to>
@@ -1478,7 +1478,7 @@
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Performance to 31 July 2026</a:t>
+            <a:t>Performance to 31 August 2026</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1495,13 +1495,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>25399</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
+      <xdr:rowOff>124883</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>14111</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>128035</xdr:rowOff>
+      <xdr:rowOff>106868</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1530,7 +1530,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25399" y="308328"/>
+          <a:off x="25399" y="287161"/>
           <a:ext cx="11969045" cy="2331485"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1630,7 +1630,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>31 July</a:t>
+            <a:t>31 August</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-GB" sz="1800" baseline="0">
@@ -1960,20 +1960,20 @@
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U39"/>
-  <sheetFormatPr defaultColWidth="7.19921875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V39"/>
+  <sheetFormatPr defaultColWidth="7.1640625" defaultRowHeight="12.95"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="12" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="3.296875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="12" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="14.796875" customWidth="1"/>
-    <col min="5" max="18" width="11.296875" customWidth="1"/>
-    <col min="19" max="19" width="3.19921875" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="18" width="11.33203125" customWidth="1"/>
+    <col min="19" max="19" width="3.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" hidden="1">
       <c r="C1" s="10">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>0</v>
@@ -2021,7 +2021,7 @@
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
     </row>
-    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" hidden="1">
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -2041,27 +2041,27 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
     </row>
-    <row r="4" spans="1:21" ht="95.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:21" ht="71.150000000000006" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:22" ht="95.1" customHeight="1"/>
+    <row r="5" spans="1:22" ht="71.099999999999994" customHeight="1">
       <c r="B5" s="12"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
       <c r="P5" s="28"/>
       <c r="Q5" s="28"/>
       <c r="R5" s="28"/>
     </row>
-    <row r="6" spans="1:21" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="18.95" customHeight="1">
       <c r="B6" s="12"/>
       <c r="C6" s="76"/>
       <c r="D6" s="76"/>
@@ -2080,27 +2080,27 @@
       <c r="Q6" s="28"/>
       <c r="R6" s="28"/>
     </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="72"/>
-    </row>
-    <row r="8" spans="1:21" ht="21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="18" customHeight="1">
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+    </row>
+    <row r="8" spans="1:22" ht="21">
       <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
@@ -2143,12 +2143,12 @@
       <c r="P8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" s="69" t="s">
+      <c r="Q8" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="R8" s="69"/>
-    </row>
-    <row r="9" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="72"/>
+    </row>
+    <row r="9" spans="1:22" s="30" customFormat="1">
       <c r="A9" s="29"/>
       <c r="C9" s="31" t="s">
         <v>29</v>
@@ -2171,8 +2171,9 @@
       <c r="S9" s="31"/>
       <c r="T9"/>
       <c r="U9"/>
-    </row>
-    <row r="10" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V9"/>
+    </row>
+    <row r="10" spans="1:22" ht="12.75" customHeight="1">
       <c r="A10" s="12" t="s">
         <v>30</v>
       </c>
@@ -2180,53 +2181,54 @@
         <v>31</v>
       </c>
       <c r="D10" s="52">
-        <v>52359.170817539998</v>
+        <v>53601.594668620004</v>
       </c>
       <c r="E10" s="53">
-        <v>5.8136777119893882E-3</v>
+        <v>1.2069804911630705E-2</v>
       </c>
       <c r="F10" s="53">
-        <v>4.1142791607133557E-2</v>
+        <v>3.1107157199089599E-2</v>
       </c>
       <c r="G10" s="53">
-        <v>5.1382444441275182E-2</v>
+        <v>4.6308420471095346E-2</v>
       </c>
       <c r="H10" s="53">
-        <v>5.8136777119893882E-3</v>
+        <v>1.7953652579422899E-2</v>
       </c>
       <c r="I10" s="53">
-        <v>0.10490884064410259</v>
+        <v>0.10084068534033083</v>
       </c>
       <c r="J10" s="53">
-        <v>0.10222587553068863</v>
+        <v>0.10806992620060404</v>
       </c>
       <c r="K10" s="53">
-        <v>0.10469681646946367</v>
+        <v>0.10802014356003435</v>
       </c>
       <c r="L10" s="53">
-        <v>7.4870860270350434E-2</v>
+        <v>7.3243572815313268E-2</v>
       </c>
       <c r="M10" s="53">
-        <v>8.6420713349612613E-2</v>
+        <v>8.8801714222398492E-2</v>
       </c>
       <c r="N10" s="53">
-        <v>9.3450148737869873E-2</v>
+        <v>9.4306812121162681E-2</v>
       </c>
       <c r="O10" s="53">
-        <v>9.7926121999992718E-2</v>
+        <v>0.10053832924624047</v>
       </c>
       <c r="P10" s="53">
-        <v>7.7704493029382218E-2</v>
+        <v>7.7173477555743206E-2</v>
       </c>
       <c r="Q10" s="53">
-        <v>8.4838667103299556E-2</v>
+        <v>8.5021284125941135E-2</v>
       </c>
       <c r="R10" s="41">
         <v>35247</v>
       </c>
       <c r="U10" s="38"/>
-    </row>
-    <row r="11" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V10" s="38"/>
+    </row>
+    <row r="11" spans="1:22" ht="12.95" customHeight="1">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -2234,53 +2236,54 @@
         <v>33</v>
       </c>
       <c r="D11" s="46">
-        <v>266337.58229039004</v>
+        <v>268148.02426069003</v>
       </c>
       <c r="E11" s="47">
-        <v>3.7861330129171649E-3</v>
+        <v>9.162464459985524E-3</v>
       </c>
       <c r="F11" s="47">
-        <v>3.6356856837471731E-2</v>
+        <v>2.6629480686595656E-2</v>
       </c>
       <c r="G11" s="47">
-        <v>4.492832999558747E-2</v>
+        <v>3.971164337832031E-2</v>
       </c>
       <c r="H11" s="47">
-        <v>3.7861330129171649E-3</v>
+        <v>1.298328778207432E-2</v>
       </c>
       <c r="I11" s="47">
-        <v>8.831249669388376E-2</v>
+        <v>8.4458936294144027E-2</v>
       </c>
       <c r="J11" s="47">
-        <v>8.8405632036682766E-2</v>
+        <v>9.1785084834094796E-2</v>
       </c>
       <c r="K11" s="47">
-        <v>8.9668672293749072E-2</v>
+        <v>9.1877403073721844E-2</v>
       </c>
       <c r="L11" s="47">
-        <v>6.4080629998463229E-2</v>
+        <v>6.2544109892306771E-2</v>
       </c>
       <c r="M11" s="47">
-        <v>7.3727345104812339E-2</v>
+        <v>7.504774225986531E-2</v>
       </c>
       <c r="N11" s="47">
-        <v>8.2034864513670938E-2</v>
+        <v>8.2670942551451548E-2</v>
       </c>
       <c r="O11" s="47">
-        <v>8.7814022922344581E-2</v>
+        <v>8.9701227921958115E-2</v>
       </c>
       <c r="P11" s="47">
-        <v>7.3340107156177461E-2</v>
+        <v>7.2771959794668994E-2</v>
       </c>
       <c r="Q11" s="47">
-        <v>9.2697795916914336E-2</v>
+        <v>9.2740098643259994E-2</v>
       </c>
       <c r="R11" s="24">
         <v>31260</v>
       </c>
       <c r="U11" s="38"/>
-    </row>
-    <row r="12" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V11" s="38"/>
+    </row>
+    <row r="12" spans="1:22" ht="12.95" customHeight="1">
       <c r="A12" s="12" t="s">
         <v>34</v>
       </c>
@@ -2288,53 +2291,54 @@
         <v>35</v>
       </c>
       <c r="D12" s="48">
-        <v>3216.3469841300002</v>
+        <v>3221.7452449299999</v>
       </c>
       <c r="E12" s="49">
-        <v>-1.5616069755315719E-3</v>
+        <v>7.9440546448471816E-3</v>
       </c>
       <c r="F12" s="49">
-        <v>4.2072670534916166E-2</v>
+        <v>2.4794610377640407E-2</v>
       </c>
       <c r="G12" s="49">
-        <v>4.034200544806292E-2</v>
+        <v>3.5356136564457866E-2</v>
       </c>
       <c r="H12" s="49">
-        <v>-1.5616069755315719E-3</v>
+        <v>6.3700421781682131E-3</v>
       </c>
       <c r="I12" s="49">
-        <v>7.5631041429962936E-2</v>
+        <v>7.1168626177624664E-2</v>
       </c>
       <c r="J12" s="49">
-        <v>8.2498725547817786E-2</v>
+        <v>8.4316360242061364E-2</v>
       </c>
       <c r="K12" s="49">
-        <v>8.6803152990178017E-2</v>
+        <v>8.9327457651450226E-2</v>
       </c>
       <c r="L12" s="49">
-        <v>5.9571078145438008E-2</v>
+        <v>5.6582015416038522E-2</v>
       </c>
       <c r="M12" s="49">
-        <v>6.475100209124314E-2</v>
+        <v>6.706720981647829E-2</v>
       </c>
       <c r="N12" s="49">
-        <v>7.3563911962997622E-2</v>
+        <v>7.3592220624871349E-2</v>
       </c>
       <c r="O12" s="49">
-        <v>8.2928007104014281E-2</v>
+        <v>8.4755166567765328E-2</v>
       </c>
       <c r="P12" s="49">
-        <v>6.9304392764596143E-2</v>
+        <v>6.9152438160794291E-2</v>
       </c>
       <c r="Q12" s="49">
-        <v>7.0307938108724377E-2</v>
+        <v>7.0399882577276751E-2</v>
       </c>
       <c r="R12" s="25">
         <v>37165</v>
       </c>
       <c r="U12" s="38"/>
-    </row>
-    <row r="13" spans="1:21" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V12" s="38"/>
+    </row>
+    <row r="13" spans="1:22" ht="12.6" customHeight="1">
       <c r="A13" s="12" t="s">
         <v>36</v>
       </c>
@@ -2342,51 +2346,52 @@
         <v>37</v>
       </c>
       <c r="D13" s="46">
-        <v>4647.1092939099999</v>
+        <v>4697.6287786700004</v>
       </c>
       <c r="E13" s="47">
-        <v>2.5845044875214655E-3</v>
+        <v>8.386804045988426E-3</v>
       </c>
       <c r="F13" s="47">
-        <v>4.0832109232833376E-2</v>
+        <v>2.3314538736661432E-2</v>
       </c>
       <c r="G13" s="47">
-        <v>4.3525336360574617E-2</v>
+        <v>3.7960116402691188E-2</v>
       </c>
       <c r="H13" s="47">
-        <v>2.5845044875214655E-3</v>
+        <v>1.099298426620271E-2</v>
       </c>
       <c r="I13" s="47">
-        <v>7.5504326791811224E-2</v>
+        <v>6.9914675015194494E-2</v>
       </c>
       <c r="J13" s="47">
-        <v>9.2491238607380344E-2</v>
+        <v>9.533511368307919E-2</v>
       </c>
       <c r="K13" s="47">
-        <v>0.10270171154695648</v>
+        <v>0.10522551412102861</v>
       </c>
       <c r="L13" s="47">
-        <v>7.1083801617579545E-2</v>
+        <v>6.9027203936041934E-2</v>
       </c>
       <c r="M13" s="47">
-        <v>7.7758702130652585E-2</v>
+        <v>7.9802326933586035E-2</v>
       </c>
       <c r="N13" s="47">
-        <v>7.9974752946569555E-2</v>
+        <v>8.0701443603471743E-2</v>
       </c>
       <c r="O13" s="47">
-        <v>7.8777645021255976E-2</v>
+        <v>8.0694702992322495E-2</v>
       </c>
       <c r="P13" s="47"/>
       <c r="Q13" s="47">
-        <v>7.6991707606480983E-2</v>
+        <v>7.7137317431364219E-2</v>
       </c>
       <c r="R13" s="26">
         <v>40725</v>
       </c>
       <c r="U13" s="38"/>
-    </row>
-    <row r="14" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V13" s="38"/>
+    </row>
+    <row r="14" spans="1:22" ht="12.95" customHeight="1">
       <c r="A14" s="12" t="s">
         <v>38</v>
       </c>
@@ -2394,51 +2399,52 @@
         <v>39</v>
       </c>
       <c r="D14" s="48">
-        <v>7458.2295022200005</v>
+        <v>7442.6599516400001</v>
       </c>
       <c r="E14" s="49">
-        <v>2.2929199933472374E-3</v>
+        <v>7.0561312210485044E-3</v>
       </c>
       <c r="F14" s="49">
-        <v>3.0998349395647311E-2</v>
+        <v>2.167445252899991E-2</v>
       </c>
       <c r="G14" s="49">
-        <v>3.7478827930514082E-2</v>
+        <v>3.3057132660072444E-2</v>
       </c>
       <c r="H14" s="49">
-        <v>2.2929199933472374E-3</v>
+        <v>9.3652303587481653E-3</v>
       </c>
       <c r="I14" s="49">
-        <v>7.4106051052793442E-2</v>
+        <v>7.0384738820875356E-2</v>
       </c>
       <c r="J14" s="49">
-        <v>7.630748821635927E-2</v>
+        <v>7.7907869585484568E-2</v>
       </c>
       <c r="K14" s="49">
-        <v>7.5225468339258306E-2</v>
+        <v>7.6598087394635028E-2</v>
       </c>
       <c r="L14" s="49">
-        <v>4.9630740555426683E-2</v>
+        <v>4.8682248797090419E-2</v>
       </c>
       <c r="M14" s="49">
-        <v>5.6758323198447237E-2</v>
+        <v>5.7126574011870004E-2</v>
       </c>
       <c r="N14" s="49">
-        <v>6.3453904364556571E-2</v>
+        <v>6.3910229583729897E-2</v>
       </c>
       <c r="O14" s="49">
-        <v>7.1562780520422142E-2</v>
+        <v>7.2756932281311165E-2</v>
       </c>
       <c r="P14" s="49"/>
       <c r="Q14" s="49">
-        <v>5.9341342861008645E-2</v>
+        <v>5.946031576820391E-2</v>
       </c>
       <c r="R14" s="25">
         <v>39326</v>
       </c>
       <c r="U14" s="38"/>
-    </row>
-    <row r="15" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V14" s="38"/>
+    </row>
+    <row r="15" spans="1:22" ht="12.95" customHeight="1">
       <c r="A15" s="12" t="s">
         <v>40</v>
       </c>
@@ -2446,53 +2452,54 @@
         <v>41</v>
       </c>
       <c r="D15" s="50">
-        <v>4824.1661643100006</v>
+        <v>4777.0241783199999</v>
       </c>
       <c r="E15" s="51">
-        <v>7.238682335175173E-4</v>
+        <v>4.4162747860181121E-3</v>
       </c>
       <c r="F15" s="51">
-        <v>2.2817323770349694E-2</v>
+        <v>1.4537097563388245E-2</v>
       </c>
       <c r="G15" s="51">
-        <v>2.7299881999344151E-2</v>
+        <v>2.259763156150758E-2</v>
       </c>
       <c r="H15" s="51">
-        <v>7.238682335175173E-4</v>
+        <v>5.1433398205637127E-3</v>
       </c>
       <c r="I15" s="51">
-        <v>5.5967261377505149E-2</v>
+        <v>5.2460855012208471E-2</v>
       </c>
       <c r="J15" s="51">
-        <v>6.0627757791251659E-2</v>
+        <v>6.038254795428033E-2</v>
       </c>
       <c r="K15" s="51">
-        <v>5.838549627881591E-2</v>
+        <v>5.8955594102952133E-2</v>
       </c>
       <c r="L15" s="51">
-        <v>3.6249735007318019E-2</v>
+        <v>3.5866414471040539E-2</v>
       </c>
       <c r="M15" s="51">
-        <v>4.0010049103055716E-2</v>
+        <v>3.964113742930378E-2</v>
       </c>
       <c r="N15" s="51">
-        <v>4.6946988733352672E-2</v>
+        <v>4.7124863259804875E-2</v>
       </c>
       <c r="O15" s="51">
-        <v>5.5625818558484044E-2</v>
+        <v>5.5984145086340038E-2</v>
       </c>
       <c r="P15" s="51">
-        <v>5.3992115749522937E-2</v>
+        <v>5.373811231809416E-2</v>
       </c>
       <c r="Q15" s="51">
-        <v>5.7936110977522527E-2</v>
+        <v>5.7920124424838237E-2</v>
       </c>
       <c r="R15" s="27">
         <v>37165</v>
       </c>
       <c r="U15" s="38"/>
-    </row>
-    <row r="16" spans="1:21" s="30" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V15" s="38"/>
+    </row>
+    <row r="16" spans="1:22" s="30" customFormat="1" ht="15.95" customHeight="1">
       <c r="A16" s="29"/>
       <c r="C16" s="31" t="s">
         <v>42</v>
@@ -2514,8 +2521,9 @@
       <c r="R16" s="32"/>
       <c r="S16" s="33"/>
       <c r="U16" s="38"/>
-    </row>
-    <row r="17" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V16" s="38"/>
+    </row>
+    <row r="17" spans="1:22" ht="12.95" customHeight="1">
       <c r="A17" s="12" t="s">
         <v>43</v>
       </c>
@@ -2523,53 +2531,54 @@
         <v>44</v>
       </c>
       <c r="D17" s="52">
-        <v>9610.5489473399994</v>
+        <v>9874.6126533400002</v>
       </c>
       <c r="E17" s="53">
-        <v>1.8749873776292465E-2</v>
+        <v>2.2136898126383527E-2</v>
       </c>
       <c r="F17" s="53">
-        <v>3.7379795887336545E-2</v>
+        <v>4.5360714569344783E-2</v>
       </c>
       <c r="G17" s="53">
-        <v>4.3921062031166129E-2</v>
+        <v>1.7552240501722622E-2</v>
       </c>
       <c r="H17" s="53">
-        <v>1.8749873776292465E-2</v>
+        <v>4.1301835948344329E-2</v>
       </c>
       <c r="I17" s="53">
-        <v>0.10025075927284481</v>
+        <v>9.4757916918292898E-2</v>
       </c>
       <c r="J17" s="53">
-        <v>0.10727412162015253</v>
+        <v>0.11650402317063017</v>
       </c>
       <c r="K17" s="53">
-        <v>0.11650553951638491</v>
+        <v>0.12488000895287715</v>
       </c>
       <c r="L17" s="53">
-        <v>9.8784657339288595E-2</v>
+        <v>9.7655256847581917E-2</v>
       </c>
       <c r="M17" s="53">
-        <v>9.6264071014817224E-2</v>
+        <v>0.10205545453941973</v>
       </c>
       <c r="N17" s="53">
-        <v>0.10114556238694722</v>
+        <v>0.10468888693948324</v>
       </c>
       <c r="O17" s="53">
-        <v>0.10293643197967983</v>
+        <v>0.10634624135041164</v>
       </c>
       <c r="P17" s="53">
-        <v>8.3730211654533426E-2</v>
+        <v>8.3319686142458868E-2</v>
       </c>
       <c r="Q17" s="53">
-        <v>9.6394784280364021E-2</v>
+        <v>9.696799730364157E-2</v>
       </c>
       <c r="R17" s="55">
         <v>36434</v>
       </c>
       <c r="U17" s="38"/>
-    </row>
-    <row r="18" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V17" s="38"/>
+    </row>
+    <row r="18" spans="1:22" ht="12.95" customHeight="1">
       <c r="A18" s="12" t="s">
         <v>45</v>
       </c>
@@ -2577,53 +2586,54 @@
         <v>46</v>
       </c>
       <c r="D18" s="56">
-        <v>11439.471193670001</v>
+        <v>11594.549893670001</v>
       </c>
       <c r="E18" s="57">
-        <v>-5.1896081160093168E-3</v>
+        <v>3.1448730938107342E-3</v>
       </c>
       <c r="F18" s="57">
-        <v>6.9611565432062344E-2</v>
+        <v>2.8993968174692703E-2</v>
       </c>
       <c r="G18" s="57">
-        <v>6.9852844316022497E-2</v>
+        <v>8.0486577247439933E-2</v>
       </c>
       <c r="H18" s="57">
-        <v>-5.1896081160093168E-3</v>
+        <v>-2.0610556811300421E-3</v>
       </c>
       <c r="I18" s="57">
-        <v>0.10934799963079794</v>
+        <v>0.10213057789125175</v>
       </c>
       <c r="J18" s="57">
-        <v>0.12373763703994499</v>
+        <v>0.13290584219204477</v>
       </c>
       <c r="K18" s="57">
-        <v>0.14323387735504345</v>
+        <v>0.14020330572971745</v>
       </c>
       <c r="L18" s="57">
-        <v>8.80331730139194E-2</v>
+        <v>8.41529153538213E-2</v>
       </c>
       <c r="M18" s="57">
-        <v>0.11699695481746727</v>
+        <v>0.11692665051334461</v>
       </c>
       <c r="N18" s="57">
-        <v>0.12182126686695095</v>
+        <v>0.12060952585514001</v>
       </c>
       <c r="O18" s="57">
-        <v>0.1241864451665482</v>
+        <v>0.12808424657977008</v>
       </c>
       <c r="P18" s="57">
-        <v>8.4361526788644586E-2</v>
+        <v>8.2989837486609458E-2</v>
       </c>
       <c r="Q18" s="57">
-        <v>7.1325879899464872E-2</v>
+        <v>7.1218041190505121E-2</v>
       </c>
       <c r="R18" s="44">
         <v>36434</v>
       </c>
       <c r="U18" s="38"/>
-    </row>
-    <row r="19" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V18" s="38"/>
+    </row>
+    <row r="19" spans="1:22" ht="12.95" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>47</v>
       </c>
@@ -2631,53 +2641,54 @@
         <v>48</v>
       </c>
       <c r="D19" s="58">
-        <v>1285.63219377</v>
+        <v>1267.9132201800001</v>
       </c>
       <c r="E19" s="59">
-        <v>-6.0561011773385565E-3</v>
+        <v>8.1951431261101927E-7</v>
       </c>
       <c r="F19" s="59">
-        <v>1.0628200638122641E-2</v>
+        <v>3.65296263975877E-4</v>
       </c>
       <c r="G19" s="59">
-        <v>5.2411870317907432E-3</v>
+        <v>-2.9899154902737588E-3</v>
       </c>
       <c r="H19" s="59">
-        <v>-6.0561011773385565E-3</v>
+        <v>-6.0552866260875395E-3</v>
       </c>
       <c r="I19" s="59">
-        <v>1.6365417325702739E-2</v>
+        <v>1.2188512906191775E-2</v>
       </c>
       <c r="J19" s="59">
-        <v>2.6383778129340323E-2</v>
+        <v>2.3305133676518951E-2</v>
       </c>
       <c r="K19" s="59">
-        <v>2.9672658090565966E-2</v>
+        <v>2.8811001684989377E-2</v>
       </c>
       <c r="L19" s="59">
-        <v>8.3173868689255977E-3</v>
+        <v>8.356386881523032E-3</v>
       </c>
       <c r="M19" s="59">
-        <v>1.0466803192462744E-2</v>
+        <v>9.2060359403775705E-3</v>
       </c>
       <c r="N19" s="59">
-        <v>1.8462714801220463E-2</v>
+        <v>1.7951062174197563E-2</v>
       </c>
       <c r="O19" s="59">
-        <v>3.4638240622209028E-2</v>
+        <v>3.3518849760306106E-2</v>
       </c>
       <c r="P19" s="59">
-        <v>4.1126001818009197E-2</v>
+        <v>4.0605101168462616E-2</v>
       </c>
       <c r="Q19" s="59">
-        <v>4.665591268877628E-2</v>
+        <v>4.6506865724591132E-2</v>
       </c>
       <c r="R19" s="43">
         <v>36342</v>
       </c>
       <c r="U19" s="38"/>
-    </row>
-    <row r="20" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V19" s="38"/>
+    </row>
+    <row r="20" spans="1:22" ht="12.95" customHeight="1">
       <c r="A20" s="12" t="s">
         <v>49</v>
       </c>
@@ -2685,53 +2696,54 @@
         <v>50</v>
       </c>
       <c r="D20" s="60">
-        <v>8559.1451235799996</v>
+        <v>8280.2863877100008</v>
       </c>
       <c r="E20" s="61">
-        <v>3.8458565276452603E-3</v>
+        <v>3.6562350592770844E-3</v>
       </c>
       <c r="F20" s="61">
-        <v>1.074807915399195E-2</v>
+        <v>1.1289870588666089E-2</v>
       </c>
       <c r="G20" s="61">
-        <v>2.0119272563165556E-2</v>
+        <v>2.0992786907660561E-2</v>
       </c>
       <c r="H20" s="61">
-        <v>3.8458565276452603E-3</v>
+        <v>7.5161529423916707E-3</v>
       </c>
       <c r="I20" s="61">
-        <v>3.8283202941565855E-2</v>
+        <v>3.9061015880249718E-2</v>
       </c>
       <c r="J20" s="61">
-        <v>4.046120051680549E-2</v>
+        <v>4.0431549033541098E-2</v>
       </c>
       <c r="K20" s="61">
-        <v>4.044002478695128E-2</v>
+        <v>4.0591068773476659E-2</v>
       </c>
       <c r="L20" s="61">
-        <v>3.0513146286060409E-2</v>
+        <v>3.1278799832963201E-2</v>
       </c>
       <c r="M20" s="61">
-        <v>2.3248897626574658E-2</v>
+        <v>2.3625464100176508E-2</v>
       </c>
       <c r="N20" s="61">
-        <v>2.2035430803754016E-2</v>
+        <v>2.2226942310058832E-2</v>
       </c>
       <c r="O20" s="61">
-        <v>2.4375040812970119E-2</v>
+        <v>2.4344475140603953E-2</v>
       </c>
       <c r="P20" s="61">
-        <v>3.0887102984990384E-2</v>
+        <v>3.0841203846075957E-2</v>
       </c>
       <c r="Q20" s="61">
-        <v>3.4331012710109486E-2</v>
+        <v>3.4361068037941526E-2</v>
       </c>
       <c r="R20" s="62">
         <v>36434</v>
       </c>
       <c r="U20" s="38"/>
-    </row>
-    <row r="21" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V20" s="38"/>
+    </row>
+    <row r="21" spans="1:22" ht="18" customHeight="1">
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -2751,10 +2763,10 @@
       <c r="R21" s="13"/>
       <c r="S21" s="13"/>
     </row>
-    <row r="22" spans="1:21" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" ht="35.1" customHeight="1">
       <c r="B22" s="13"/>
       <c r="C22" s="74" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D22" s="74"/>
       <c r="E22" s="74"/>
@@ -2773,10 +2785,10 @@
       <c r="R22" s="74"/>
       <c r="S22" s="13"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22">
       <c r="B23" s="13"/>
       <c r="C23" s="19" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20"/>
@@ -2795,10 +2807,10 @@
       <c r="R23" s="21"/>
       <c r="S23" s="13"/>
     </row>
-    <row r="24" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" ht="36" customHeight="1">
       <c r="B24" s="13"/>
       <c r="C24" s="74" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D24" s="74"/>
       <c r="E24" s="74"/>
@@ -2817,9 +2829,9 @@
       <c r="R24" s="74"/>
       <c r="S24" s="13"/>
     </row>
-    <row r="25" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" ht="17.25" customHeight="1">
       <c r="C25" s="75" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D25" s="75"/>
       <c r="E25" s="75"/>
@@ -2839,9 +2851,9 @@
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
     </row>
-    <row r="26" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" ht="39" customHeight="1">
       <c r="C26" s="73" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D26" s="73"/>
       <c r="E26" s="73"/>
@@ -2860,27 +2872,27 @@
       <c r="R26" s="23"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="72"/>
-      <c r="Q27" s="72"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="72"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22">
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="71"/>
+      <c r="S27" s="71"/>
+    </row>
+    <row r="28" spans="1:22">
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -2898,7 +2910,7 @@
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
     </row>
-    <row r="29" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" ht="26.1" customHeight="1">
       <c r="C29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
@@ -2915,7 +2927,7 @@
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
     </row>
-    <row r="30" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" ht="26.1" customHeight="1">
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -2933,7 +2945,7 @@
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
     </row>
-    <row r="31" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="26.1" customHeight="1">
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -2951,7 +2963,7 @@
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
     </row>
-    <row r="32" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" ht="26.1" customHeight="1">
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
@@ -2969,7 +2981,7 @@
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
     </row>
-    <row r="33" spans="3:18" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:18" ht="26.1" customHeight="1">
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
@@ -2987,7 +2999,7 @@
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
     </row>
-    <row r="34" spans="3:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:18">
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -3005,7 +3017,7 @@
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
     </row>
-    <row r="35" spans="3:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:18">
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
@@ -3023,7 +3035,7 @@
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
     </row>
-    <row r="36" spans="3:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:18">
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -3041,7 +3053,7 @@
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
     </row>
-    <row r="37" spans="3:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:18">
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
@@ -3056,7 +3068,7 @@
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
     </row>
-    <row r="38" spans="3:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:18">
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
@@ -3071,7 +3083,7 @@
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
     </row>
-    <row r="39" spans="3:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:18">
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
@@ -3117,20 +3129,20 @@
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
-  <sheetFormatPr defaultColWidth="7.19921875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V34"/>
+  <sheetFormatPr defaultColWidth="7.1640625" defaultRowHeight="12.95"/>
   <cols>
-    <col min="1" max="1" width="0.19921875" style="12" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="3.796875" customWidth="1"/>
-    <col min="3" max="3" width="22.796875" customWidth="1"/>
-    <col min="4" max="4" width="14.796875" customWidth="1"/>
-    <col min="5" max="17" width="11.296875" customWidth="1"/>
-    <col min="18" max="18" width="2.796875" customWidth="1"/>
+    <col min="1" max="1" width="0.1640625" style="12" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="17" width="11.33203125" customWidth="1"/>
+    <col min="18" max="18" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="27" hidden="1" customHeight="1">
       <c r="C1" s="10">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>0</v>
@@ -3175,7 +3187,7 @@
       <c r="R1" s="9"/>
       <c r="S1" s="9"/>
     </row>
-    <row r="2" spans="1:19" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="18.95" hidden="1" customHeight="1">
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -3194,26 +3206,26 @@
       <c r="R2" s="9"/>
       <c r="S2" s="9"/>
     </row>
-    <row r="4" spans="1:19" ht="95.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:19" ht="71.150000000000006" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:19" ht="95.1" customHeight="1"/>
+    <row r="5" spans="1:19" ht="71.099999999999994" customHeight="1">
       <c r="B5" s="12"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
       <c r="O5" s="37"/>
       <c r="P5" s="28"/>
       <c r="Q5" s="28"/>
     </row>
-    <row r="6" spans="1:19" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="18.95" customHeight="1">
       <c r="B6" s="12"/>
       <c r="C6" s="76"/>
       <c r="D6" s="76"/>
@@ -3231,26 +3243,26 @@
       <c r="P6" s="28"/>
       <c r="Q6" s="28"/>
     </row>
-    <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-    </row>
-    <row r="8" spans="1:19" ht="21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="18" customHeight="1">
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+    </row>
+    <row r="8" spans="1:19" ht="21">
       <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
@@ -3288,14 +3300,14 @@
         <v>25</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="P8" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="Q8" s="69"/>
-    </row>
-    <row r="9" spans="1:19" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q8" s="72"/>
+    </row>
+    <row r="9" spans="1:19" s="30" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="29"/>
       <c r="C9" s="35" t="s">
         <v>29</v>
@@ -3316,305 +3328,305 @@
       <c r="Q9" s="31"/>
       <c r="R9" s="31"/>
     </row>
-    <row r="10" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="12.95" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10" s="54" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="52">
-        <v>3713.6778726900002</v>
+        <v>3862.4976410100003</v>
       </c>
       <c r="E10" s="53">
-        <v>5.6868356070370382E-3</v>
+        <v>1.3224085819194724E-2</v>
       </c>
       <c r="F10" s="53">
-        <v>4.4795369460720658E-2</v>
+        <v>3.3533800429872064E-2</v>
       </c>
       <c r="G10" s="53">
-        <v>5.6791830031760214E-2</v>
+        <v>5.0687837248314591E-2</v>
       </c>
       <c r="H10" s="53">
-        <v>5.6868356070370382E-3</v>
+        <v>1.8986124628338874E-2</v>
       </c>
       <c r="I10" s="53">
-        <v>0.11612506170115554</v>
+        <v>0.11138100375568363</v>
       </c>
       <c r="J10" s="53">
-        <v>0.11194011250887598</v>
+        <v>0.11849338692740644</v>
       </c>
       <c r="K10" s="53">
-        <v>0.1151441568272973</v>
+        <v>0.11877946060588226</v>
       </c>
       <c r="L10" s="53">
-        <v>8.2697469011039845E-2</v>
+        <v>8.1051995286640657E-2</v>
       </c>
       <c r="M10" s="53">
-        <v>9.5149320170274776E-2</v>
+        <v>9.7710513600768989E-2</v>
       </c>
       <c r="N10" s="53">
-        <v>0.1025313178186498</v>
+        <v>0.10352906271648753</v>
       </c>
       <c r="O10" s="53">
-        <v>0.10809419968776848</v>
+        <v>0.11101729920923115</v>
       </c>
       <c r="P10" s="53">
-        <v>8.1347543925162358E-2</v>
+        <v>8.1723607913009505E-2</v>
       </c>
       <c r="Q10" s="41">
         <v>39448</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="12.95" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C11" s="63" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="56">
-        <v>37405.949577860003</v>
+        <v>38284.813427230001</v>
       </c>
       <c r="E11" s="57">
-        <v>3.6582442732376926E-3</v>
+        <v>9.9421552755779123E-3</v>
       </c>
       <c r="F11" s="57">
-        <v>3.94607210814037E-2</v>
+        <v>2.8533931626304011E-2</v>
       </c>
       <c r="G11" s="57">
-        <v>4.9272822338933417E-2</v>
+        <v>4.3186744183812402E-2</v>
       </c>
       <c r="H11" s="57">
-        <v>3.6582442732376926E-3</v>
+        <v>1.3636770381416127E-2</v>
       </c>
       <c r="I11" s="57">
-        <v>9.7264289448307742E-2</v>
+        <v>9.2886237073877623E-2</v>
       </c>
       <c r="J11" s="57">
-        <v>9.6699205406640593E-2</v>
+        <v>0.10055292035133201</v>
       </c>
       <c r="K11" s="57">
-        <v>9.8288779230596049E-2</v>
+        <v>0.10070054474897744</v>
       </c>
       <c r="L11" s="57">
-        <v>7.0239096356213795E-2</v>
+        <v>6.8680571717400385E-2</v>
       </c>
       <c r="M11" s="57">
-        <v>8.0420592305426794E-2</v>
+        <v>8.183936908109346E-2</v>
       </c>
       <c r="N11" s="57">
-        <v>8.9455259021477732E-2</v>
+        <v>9.0075463405551656E-2</v>
       </c>
       <c r="O11" s="57">
-        <v>9.6922437098818023E-2</v>
+        <v>9.8920795107310583E-2</v>
       </c>
       <c r="P11" s="57">
-        <v>7.627440057367274E-2</v>
+        <v>7.6484734578543365E-2</v>
       </c>
       <c r="Q11" s="42">
         <v>39448</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="12.95" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C12" s="64" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="58">
-        <v>898.83539512000004</v>
+        <v>901.08665222000002</v>
       </c>
       <c r="E12" s="59">
-        <v>-2.0740952441462581E-3</v>
+        <v>8.6681391152242607E-3</v>
       </c>
       <c r="F12" s="59">
-        <v>4.3877640977340551E-2</v>
+        <v>2.5180612349701363E-2</v>
       </c>
       <c r="G12" s="59">
-        <v>4.2805078493881994E-2</v>
+        <v>3.691160783582375E-2</v>
       </c>
       <c r="H12" s="59">
-        <v>-2.0740952441462581E-3</v>
+        <v>6.5760653249635178E-3</v>
       </c>
       <c r="I12" s="59">
-        <v>8.1958503703531735E-2</v>
+        <v>7.6777802562231462E-2</v>
       </c>
       <c r="J12" s="59">
-        <v>8.9907681256635605E-2</v>
+        <v>9.198118993075223E-2</v>
       </c>
       <c r="K12" s="59">
-        <v>9.4851034133377435E-2</v>
+        <v>9.7608993156289306E-2</v>
       </c>
       <c r="L12" s="59">
-        <v>6.4793187030955449E-2</v>
+        <v>6.1719112767720755E-2</v>
       </c>
       <c r="M12" s="59">
-        <v>7.1029385833686759E-2</v>
+        <v>7.3567042995943729E-2</v>
       </c>
       <c r="N12" s="59">
-        <v>8.1088570207453706E-2</v>
+        <v>8.1064797865948682E-2</v>
       </c>
       <c r="O12" s="59">
-        <v>9.206737312853383E-2</v>
+        <v>9.4121732223593393E-2</v>
       </c>
       <c r="P12" s="59">
-        <v>7.2213517832665261E-2</v>
+        <v>7.2369022911127706E-2</v>
       </c>
       <c r="Q12" s="43">
         <v>39448</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="12.6" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C13" s="63" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="56">
-        <v>2160.85718898</v>
+        <v>2231.7921499099998</v>
       </c>
       <c r="E13" s="57">
-        <v>2.6319895755108741E-3</v>
+        <v>9.1585106961653388E-3</v>
       </c>
       <c r="F13" s="57">
-        <v>4.4950382229435495E-2</v>
+        <v>2.5473278891754873E-2</v>
       </c>
       <c r="G13" s="57">
-        <v>4.8680294534714334E-2</v>
+        <v>4.2070437395442084E-2</v>
       </c>
       <c r="H13" s="57">
-        <v>2.6319895755108741E-3</v>
+        <v>1.1814605376355725E-2</v>
       </c>
       <c r="I13" s="57">
-        <v>8.3680189412588521E-2</v>
+        <v>7.7191429417481944E-2</v>
       </c>
       <c r="J13" s="57">
-        <v>0.10316326912927436</v>
+        <v>0.10641880554451065</v>
       </c>
       <c r="K13" s="57">
-        <v>0.11445681747676004</v>
+        <v>0.11721198511484207</v>
       </c>
       <c r="L13" s="57">
-        <v>7.9283367183027725E-2</v>
+        <v>7.6994951254255928E-2</v>
       </c>
       <c r="M13" s="57">
-        <v>8.6687151897893708E-2</v>
+        <v>8.8976597921386638E-2</v>
       </c>
       <c r="N13" s="57">
-        <v>8.972487052855152E-2</v>
+        <v>9.0573345938289931E-2</v>
       </c>
       <c r="O13" s="57"/>
       <c r="P13" s="57">
-        <v>9.3383482622449401E-2</v>
+        <v>9.3496531523454315E-2</v>
       </c>
       <c r="Q13" s="44">
         <v>40849</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="12.95" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C14" s="64" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="58">
-        <v>9322.9797261000003</v>
+        <v>9495.6024483300007</v>
       </c>
       <c r="E14" s="59">
-        <v>2.0453109413908631E-3</v>
+        <v>7.7796087634850984E-3</v>
       </c>
       <c r="F14" s="59">
-        <v>3.410730909858431E-2</v>
+        <v>2.3495423199711249E-2</v>
       </c>
       <c r="G14" s="59">
-        <v>4.1731060184377375E-2</v>
+        <v>3.6496655284232453E-2</v>
       </c>
       <c r="H14" s="59">
-        <v>2.0453109413908631E-3</v>
+        <v>9.8408314237996581E-3</v>
       </c>
       <c r="I14" s="59">
-        <v>8.2814141110389178E-2</v>
+        <v>7.8444806545094378E-2</v>
       </c>
       <c r="J14" s="59">
-        <v>8.4812940642268256E-2</v>
+        <v>8.6660083497126256E-2</v>
       </c>
       <c r="K14" s="59">
-        <v>8.376261760204752E-2</v>
+        <v>8.5236908488632385E-2</v>
       </c>
       <c r="L14" s="59">
-        <v>5.5240771590809055E-2</v>
+        <v>5.4246550638852975E-2</v>
       </c>
       <c r="M14" s="59">
-        <v>6.3089948297157014E-2</v>
+        <v>6.3474059306860925E-2</v>
       </c>
       <c r="N14" s="59">
-        <v>7.0962272294029932E-2</v>
+        <v>7.135932235389944E-2</v>
       </c>
       <c r="O14" s="59">
-        <v>8.0518623687813193E-2</v>
+        <v>8.1907010404830075E-2</v>
       </c>
       <c r="P14" s="59">
-        <v>6.881352990125332E-2</v>
+        <v>6.8933546020515726E-2</v>
       </c>
       <c r="Q14" s="43">
         <v>39448</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="12.95" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C15" s="68" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="66">
-        <v>4445.5485859099999</v>
+        <v>4478.7735929099999</v>
       </c>
       <c r="E15" s="67">
-        <v>3.830884612145646E-4</v>
+        <v>4.9527063048359883E-3</v>
       </c>
       <c r="F15" s="67">
-        <v>2.6279439760482054E-2</v>
+        <v>1.6933383445361019E-2</v>
       </c>
       <c r="G15" s="67">
-        <v>3.1560891830278791E-2</v>
+        <v>2.6181491084302136E-2</v>
       </c>
       <c r="H15" s="67">
-        <v>3.830884612145646E-4</v>
+        <v>5.3376920906877201E-3</v>
       </c>
       <c r="I15" s="67">
-        <v>6.3678942998005805E-2</v>
+        <v>5.9768362983142739E-2</v>
       </c>
       <c r="J15" s="67">
-        <v>6.7654469096768616E-2</v>
+        <v>6.7411092103453155E-2</v>
       </c>
       <c r="K15" s="67">
-        <v>6.5390571409832482E-2</v>
+        <v>6.6001203141237599E-2</v>
       </c>
       <c r="L15" s="67">
-        <v>4.0612755991301028E-2</v>
+        <v>4.0211787740375662E-2</v>
       </c>
       <c r="M15" s="67">
-        <v>4.4503966200405955E-2</v>
+        <v>4.4088569231584759E-2</v>
       </c>
       <c r="N15" s="67">
-        <v>5.2518434867674879E-2</v>
+        <v>5.265588465497504E-2</v>
       </c>
       <c r="O15" s="67">
-        <v>6.2858187616365704E-2</v>
+        <v>6.3257219658922476E-2</v>
       </c>
       <c r="P15" s="67">
-        <v>5.866020358257705E-2</v>
+        <v>5.8665816342335836E-2</v>
       </c>
       <c r="Q15" s="45">
         <v>39448</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="30" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" s="30" customFormat="1" ht="14.1" customHeight="1">
       <c r="A16" s="29"/>
       <c r="C16" s="31" t="s">
         <v>42</v>
@@ -3635,207 +3647,207 @@
       <c r="Q16" s="32"/>
       <c r="R16" s="33"/>
     </row>
-    <row r="17" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" ht="12.95" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C17" s="54" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="52">
-        <v>1958.56689916</v>
+        <v>2050.4135632900002</v>
       </c>
       <c r="E17" s="53">
-        <v>2.0313699914751078E-2</v>
+        <v>2.396368141977287E-2</v>
       </c>
       <c r="F17" s="53">
-        <v>4.05466453695719E-2</v>
+        <v>4.9059249260494299E-2</v>
       </c>
       <c r="G17" s="53">
-        <v>4.846298175762518E-2</v>
+        <v>1.9640847304099776E-2</v>
       </c>
       <c r="H17" s="53">
-        <v>2.0313699914751078E-2</v>
+        <v>4.4764172367737907E-2</v>
       </c>
       <c r="I17" s="53">
-        <v>0.11109851284124111</v>
+        <v>0.1044949776950439</v>
       </c>
       <c r="J17" s="53">
-        <v>0.11817126268400574</v>
+        <v>0.12831785266536266</v>
       </c>
       <c r="K17" s="53">
-        <v>0.12902937917868937</v>
+        <v>0.13802643544285811</v>
       </c>
       <c r="L17" s="53">
-        <v>0.11034791261068112</v>
+        <v>0.10915903412928539</v>
       </c>
       <c r="M17" s="53">
-        <v>0.10874430123512828</v>
+        <v>0.11495038231509647</v>
       </c>
       <c r="N17" s="53">
-        <v>0.11306623706951119</v>
+        <v>0.11689930601437082</v>
       </c>
       <c r="O17" s="53">
-        <v>0.11522575655986661</v>
+        <v>0.11851302680547909</v>
       </c>
       <c r="P17" s="53">
-        <v>8.6636899382397617E-2</v>
+        <v>8.7604413342052628E-2</v>
       </c>
       <c r="Q17" s="55">
         <v>39448</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" ht="12.95" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C18" s="63" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="56">
-        <v>1691.6625562899999</v>
+        <v>1728.4879569300001</v>
       </c>
       <c r="E18" s="57">
-        <v>-5.820761503359877E-3</v>
+        <v>3.4539705542261279E-3</v>
       </c>
       <c r="F18" s="57">
-        <v>7.5435651278203189E-2</v>
+        <v>3.1467043035322544E-2</v>
       </c>
       <c r="G18" s="57">
-        <v>7.523176975423114E-2</v>
+        <v>8.706463517905659E-2</v>
       </c>
       <c r="H18" s="57">
-        <v>-5.820761503359877E-3</v>
+        <v>-2.3868956879695273E-3</v>
       </c>
       <c r="I18" s="57">
-        <v>0.11760727034601719</v>
+        <v>0.10972909743687127</v>
       </c>
       <c r="J18" s="57">
-        <v>0.13290255749552199</v>
+        <v>0.14284280021564827</v>
       </c>
       <c r="K18" s="57">
-        <v>0.15502349727413703</v>
+        <v>0.15173007968092567</v>
       </c>
       <c r="L18" s="57">
-        <v>9.4721418862745224E-2</v>
+        <v>9.0563747175518711E-2</v>
       </c>
       <c r="M18" s="57">
-        <v>0.12608582580541841</v>
+        <v>0.12598534037810488</v>
       </c>
       <c r="N18" s="57">
-        <v>0.13196050429315109</v>
+        <v>0.13060241409182127</v>
       </c>
       <c r="O18" s="57">
-        <v>0.1364416353902505</v>
+        <v>0.14099166605013952</v>
       </c>
       <c r="P18" s="57">
-        <v>9.1857009090316091E-2</v>
+        <v>9.1622304180603589E-2</v>
       </c>
       <c r="Q18" s="44">
         <v>39448</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" ht="12.95" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C19" s="64" t="s">
         <v>48</v>
       </c>
       <c r="D19" s="58">
-        <v>590.90183890999992</v>
+        <v>594.79834009000001</v>
       </c>
       <c r="E19" s="59">
-        <v>-7.138786750550471E-3</v>
+        <v>-8.5418189780066554E-5</v>
       </c>
       <c r="F19" s="59">
-        <v>1.2627945636744263E-2</v>
+        <v>3.4157536718803551E-4</v>
       </c>
       <c r="G19" s="59">
-        <v>5.9956551638702385E-3</v>
+        <v>-3.5593246142485275E-3</v>
       </c>
       <c r="H19" s="59">
-        <v>-7.138786750550471E-3</v>
+        <v>-7.2235951580890802E-3</v>
       </c>
       <c r="I19" s="59">
-        <v>1.8733240552557359E-2</v>
+        <v>1.3722242998679567E-2</v>
       </c>
       <c r="J19" s="59">
-        <v>3.0773217775875154E-2</v>
+        <v>2.7021788431249416E-2</v>
       </c>
       <c r="K19" s="59">
-        <v>3.4639331383073263E-2</v>
+        <v>3.3605228243211896E-2</v>
       </c>
       <c r="L19" s="59">
-        <v>9.3435193733171443E-3</v>
+        <v>9.307925668645068E-3</v>
       </c>
       <c r="M19" s="59">
-        <v>1.217659715147215E-2</v>
+        <v>1.0693942523812391E-2</v>
       </c>
       <c r="N19" s="59">
-        <v>2.1597239747529542E-2</v>
+        <v>2.1036261283610427E-2</v>
       </c>
       <c r="O19" s="59">
-        <v>4.0029346645011184E-2</v>
+        <v>3.8765575507725317E-2</v>
       </c>
       <c r="P19" s="59">
-        <v>4.7023698404995207E-2</v>
+        <v>4.6800177405979505E-2</v>
       </c>
       <c r="Q19" s="43">
         <v>39448</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" ht="12.95" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C20" s="65" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="60">
-        <v>3541.27179183</v>
+        <v>3548.8766306500002</v>
       </c>
       <c r="E20" s="61">
-        <v>4.057688856998861E-3</v>
+        <v>4.2594429820847724E-3</v>
       </c>
       <c r="F20" s="61">
-        <v>1.2161795938934725E-2</v>
+        <v>1.2722527550434929E-2</v>
       </c>
       <c r="G20" s="61">
-        <v>2.3081151228454177E-2</v>
+        <v>2.4175288680767321E-2</v>
       </c>
       <c r="H20" s="61">
-        <v>4.057688856998861E-3</v>
+        <v>8.3344153334090603E-3</v>
       </c>
       <c r="I20" s="61">
-        <v>4.4264823213768935E-2</v>
+        <v>4.5133776572813547E-2</v>
       </c>
       <c r="J20" s="61">
-        <v>4.6625472263896448E-2</v>
+        <v>4.6631218356770879E-2</v>
       </c>
       <c r="K20" s="61">
-        <v>4.6851001874105735E-2</v>
+        <v>4.7003647375651582E-2</v>
       </c>
       <c r="L20" s="61">
-        <v>3.524449883481022E-2</v>
+        <v>3.6124430703919512E-2</v>
       </c>
       <c r="M20" s="61">
-        <v>2.6997040351444655E-2</v>
+        <v>2.7436412093498428E-2</v>
       </c>
       <c r="N20" s="61">
-        <v>2.5709321905094163E-2</v>
+        <v>2.5936470869448745E-2</v>
       </c>
       <c r="O20" s="61">
-        <v>2.847360925848207E-2</v>
+        <v>2.8429286793702307E-2</v>
       </c>
       <c r="P20" s="61">
-        <v>3.3291095708815131E-2</v>
+        <v>3.3372358449103134E-2</v>
       </c>
       <c r="Q20" s="62">
         <v>39448</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" ht="18" customHeight="1">
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -3854,10 +3866,10 @@
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
     </row>
-    <row r="22" spans="1:21" s="17" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" s="17" customFormat="1" ht="26.1" customHeight="1">
       <c r="A22" s="16"/>
       <c r="B22" s="78" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C22" s="78"/>
       <c r="D22" s="78"/>
@@ -3875,7 +3887,7 @@
       <c r="P22" s="78"/>
       <c r="Q22" s="78"/>
     </row>
-    <row r="23" spans="1:21" s="17" customFormat="1" ht="2.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" s="17" customFormat="1" ht="2.4500000000000002" customHeight="1">
       <c r="A23" s="16"/>
       <c r="B23" s="78"/>
       <c r="C23" s="78"/>
@@ -3894,10 +3906,10 @@
       <c r="P23" s="78"/>
       <c r="Q23" s="78"/>
     </row>
-    <row r="24" spans="1:21" s="17" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" s="17" customFormat="1" ht="28.5" customHeight="1">
       <c r="A24" s="16"/>
       <c r="B24" s="78" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C24" s="78"/>
       <c r="D24" s="78"/>
@@ -3915,10 +3927,10 @@
       <c r="P24" s="78"/>
       <c r="Q24" s="78"/>
     </row>
-    <row r="25" spans="1:21" s="17" customFormat="1" ht="12.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" s="17" customFormat="1" ht="12.6">
       <c r="A25" s="16"/>
       <c r="B25" s="79" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C25" s="79"/>
       <c r="D25" s="79"/>
@@ -3936,10 +3948,10 @@
       <c r="P25" s="79"/>
       <c r="Q25" s="79"/>
     </row>
-    <row r="26" spans="1:21" s="17" customFormat="1" ht="41.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" s="17" customFormat="1" ht="41.45" customHeight="1">
       <c r="A26" s="16"/>
       <c r="B26" s="80" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C26" s="80"/>
       <c r="D26" s="80"/>
@@ -3957,7 +3969,7 @@
       <c r="P26" s="80"/>
       <c r="Q26" s="80"/>
     </row>
-    <row r="27" spans="1:21" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" ht="39" customHeight="1">
       <c r="C27" s="77"/>
       <c r="D27" s="77"/>
       <c r="E27" s="77"/>
@@ -3975,30 +3987,31 @@
       <c r="Q27" s="77"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
-      <c r="R28" s="72"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22">
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="71"/>
+    </row>
+    <row r="29" spans="1:22">
       <c r="T29" s="77"/>
       <c r="U29" s="77"/>
-    </row>
-    <row r="30" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V29" s="77"/>
+    </row>
+    <row r="30" spans="1:22" ht="26.1" customHeight="1">
       <c r="C30" s="81"/>
       <c r="D30" s="81"/>
       <c r="E30" s="81"/>
@@ -4015,7 +4028,7 @@
       <c r="P30" s="81"/>
       <c r="Q30" s="81"/>
     </row>
-    <row r="31" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="26.1" customHeight="1">
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
       <c r="E31" s="81"/>
@@ -4032,7 +4045,7 @@
       <c r="P31" s="81"/>
       <c r="Q31" s="81"/>
     </row>
-    <row r="32" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" ht="26.1" customHeight="1">
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
       <c r="E32" s="81"/>
@@ -4049,7 +4062,7 @@
       <c r="P32" s="81"/>
       <c r="Q32" s="81"/>
     </row>
-    <row r="33" spans="3:17" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:17" ht="26.1" customHeight="1">
       <c r="C33" s="81"/>
       <c r="D33" s="81"/>
       <c r="E33" s="81"/>
@@ -4066,10 +4079,10 @@
       <c r="P33" s="81"/>
       <c r="Q33" s="81"/>
     </row>
-    <row r="34" spans="3:17" ht="26.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="3:17" ht="26.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T29:V29"/>
     <mergeCell ref="C30:Q30"/>
     <mergeCell ref="C31:Q31"/>
     <mergeCell ref="C32:Q32"/>
@@ -4114,6 +4127,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005DC95613170AD541A1ACA0E893584A98" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3b58b6af8c26e0dae27f7873f3072402">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="05c3b009-07a7-41e1-9067-dad62aaf44d0" xmlns:ns3="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v4" xmlns:ns5="2e38548d-c34f-4b92-b5e4-1a6d88eeb1ff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fa8d5a8e80a87f753beebba1ea9c5782" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4468,15 +4540,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_dlc_DocId xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">MEM020-1928282007-980616</_dlc_DocId>
+    <TaxCatchAll xmlns="2e38548d-c34f-4b92-b5e4-1a6d88eeb1ff" xsi:nil="true"/>
+    <_dlc_DocId xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">MEM020-1928282007-985978</_dlc_DocId>
     <_dlc_DocIdUrl xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">
-      <Url>https://australiansuper.sharepoint.com/teams/MEMMarketing/_layouts/15/DocIdRedir.aspx?ID=MEM020-1928282007-980616</Url>
-      <Description>MEM020-1928282007-980616</Description>
+      <Url>https://australiansuper.sharepoint.com/teams/MEMMarketing/_layouts/15/DocIdRedir.aspx?ID=MEM020-1928282007-985978</Url>
+      <Description>MEM020-1928282007-985978</Description>
     </_dlc_DocIdUrl>
     <SharedWithUsers xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0">
       <UserInfo>
@@ -4505,15 +4578,14 @@
         <AccountType/>
       </UserInfo>
     </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
     <NextReviewDate xmlns="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018" xsi:nil="true"/>
     <_Flow_SignoffStatus xmlns="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018" xsi:nil="true"/>
     <Notes xmlns="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018" xsi:nil="true"/>
-    <TaxCatchAll xmlns="2e38548d-c34f-4b92-b5e4-1a6d88eeb1ff" xsi:nil="true"/>
     <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
     <Updatetriggers xmlns="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
     <_dlc_DocIdPersistId xmlns="05c3b009-07a7-41e1-9067-dad62aaf44d0" xsi:nil="true"/>
     <Owner xmlns="11442ef6-cd2a-47d3-a3d2-fc18bf8f4018">
       <UserInfo>
@@ -4526,101 +4598,20 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A4B1A7-5047-4890-AD37-81F58F19DF32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D7DB65-0DC2-4D64-A74D-4D73CCCADE99}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A0CFC47-C21A-4C13-ADDE-45F0CE497741}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c5064bf2-310c-4cc7-a1bf-7de2b6fc5997"/>
-    <ds:schemaRef ds:uri="eaf2e70e-2c74-47e4-9f5b-aeff8bab5ce2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F1476A-B5B9-40EF-A53E-6CD6A17FAC54}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D7DB65-0DC2-4D64-A74D-4D73CCCADE99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB1726D-1DA2-4081-82C6-D43A4CB65EFA}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F1476A-B5B9-40EF-A53E-6CD6A17FAC54}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A0CFC47-C21A-4C13-ADDE-45F0CE497741}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
